--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.54385</v>
+        <v>17.09372</v>
       </c>
       <c r="D2" t="n">
-        <v>16.34826</v>
+        <v>16.54135</v>
       </c>
       <c r="E2" t="n">
-        <v>16.37347</v>
+        <v>16.60235</v>
       </c>
       <c r="F2" t="n">
-        <v>42.56986</v>
+        <v>42.657</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04987</v>
+        <v>0.05056</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80645</v>
+        <v>1.8134</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.4148</v>
+        <v>16.86494</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73531</v>
+        <v>16.66318</v>
       </c>
       <c r="E3" t="n">
-        <v>16.62317</v>
+        <v>16.8586</v>
       </c>
       <c r="F3" t="n">
-        <v>42.37886</v>
+        <v>41.44784</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05147</v>
+        <v>0.05151</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80244</v>
+        <v>1.82497</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.64156</v>
+        <v>17.00037</v>
       </c>
       <c r="D4" t="n">
-        <v>16.78096</v>
+        <v>16.80326</v>
       </c>
       <c r="E4" t="n">
-        <v>16.34965</v>
+        <v>16.99498</v>
       </c>
       <c r="F4" t="n">
-        <v>42.06159</v>
+        <v>42.65151</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05047</v>
+        <v>0.05141</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82639</v>
+        <v>1.78641</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89748</v>
+        <v>16.8608</v>
       </c>
       <c r="D6" t="n">
-        <v>16.12967</v>
+        <v>16.27518</v>
       </c>
       <c r="E6" t="n">
-        <v>16.90508</v>
+        <v>16.43428</v>
       </c>
       <c r="F6" t="n">
-        <v>22.10115</v>
+        <v>21.35688</v>
       </c>
       <c r="G6" t="n">
-        <v>34.43529</v>
+        <v>34.33773</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.50428</v>
+        <v>16.96177</v>
       </c>
       <c r="D7" t="n">
-        <v>16.15218</v>
+        <v>15.98247</v>
       </c>
       <c r="E7" t="n">
-        <v>16.40627</v>
+        <v>16.71157</v>
       </c>
       <c r="F7" t="n">
-        <v>21.94599</v>
+        <v>21.36539</v>
       </c>
       <c r="G7" t="n">
-        <v>33.76736</v>
+        <v>33.15527</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83208</v>
+        <v>16.92811</v>
       </c>
       <c r="D8" t="n">
-        <v>15.88704</v>
+        <v>16.14931</v>
       </c>
       <c r="E8" t="n">
-        <v>16.70418</v>
+        <v>16.38152</v>
       </c>
       <c r="F8" t="n">
-        <v>21.81479</v>
+        <v>22.12736</v>
       </c>
       <c r="G8" t="n">
-        <v>33.93706</v>
+        <v>34.35948</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6061</v>
+        <v>0.60106</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14671</v>
+        <v>1.13618</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6077</v>
+        <v>0.60154</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12213</v>
+        <v>1.1312</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6005200000000001</v>
+        <v>0.60419</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12753</v>
+        <v>1.11157</v>
       </c>
     </row>
   </sheetData>
